--- a/tests/fixtures/21_monthly_budget/data-export-control.xlsx
+++ b/tests/fixtures/21_monthly_budget/data-export-control.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -768,1889 +768,1890 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Mortgage or rent</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-46</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>-12</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F19" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>-6</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Water and sewer</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Cable</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F21" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Waste removal</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Maintenance or repairs</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Supplies</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n">
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n">
         <v>-41</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B28" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Night out</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Music platforms</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Movies</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Concerts</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Sporting events</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Live theater</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B40" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Credit card</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Credit card</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Credit card</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B49" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Vehicle payment</t>
         </is>
       </c>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Bus/taxi fare</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Licensing</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n"/>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n"/>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n"/>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B59" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="n"/>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n"/>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="n"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B66" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="n"/>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Life</t>
         </is>
       </c>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="n"/>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n"/>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
-      <c r="G70" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B73" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="n"/>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="4" t="n"/>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Retirement account</t>
         </is>
       </c>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Investment account</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="n"/>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="n"/>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
-      <c r="G76" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B79" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="4" t="n"/>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Dining out</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n"/>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="n"/>
+      <c r="G81" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n"/>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="n"/>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B85" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="n"/>
-      <c r="B85" s="4" t="n"/>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="4" t="n"/>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Charity 1</t>
         </is>
       </c>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="4" t="n"/>
-      <c r="G85" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Charity 2</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="n"/>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n"/>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Charity 3</t>
         </is>
       </c>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="n"/>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
+      <c r="B91" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="n"/>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="4" t="n"/>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="n"/>
-      <c r="B93" s="4" t="n"/>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+      <c r="G93" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n"/>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Grooming</t>
         </is>
       </c>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
-      <c r="G94" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="n"/>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="n"/>
+      <c r="G95" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n"/>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8" t="n"/>
-      <c r="G96" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B99" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="4" t="n"/>
-      <c r="B99" s="4" t="n"/>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="4" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>Attorney</t>
         </is>
       </c>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>Alimony</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="n"/>
-      <c r="B101" s="4" t="n"/>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n"/>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>Payments on lien or judgment</t>
         </is>
       </c>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="n"/>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B105" s="3" t="n">
+      <c r="B106" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="4" t="n"/>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="4" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="n"/>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>Hair/nails</t>
         </is>
       </c>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
-      <c r="G107" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="n"/>
-      <c r="B108" s="4" t="n"/>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="E108" s="6" t="n"/>
+      <c r="F108" s="6" t="n"/>
+      <c r="G108" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="n"/>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>Dry cleaning</t>
         </is>
       </c>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
-      <c r="G109" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="n"/>
-      <c r="B110" s="4" t="n"/>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="6" t="n"/>
+      <c r="G110" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n"/>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>Health club</t>
         </is>
       </c>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="n"/>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>Organization dues or fees</t>
         </is>
       </c>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
-      <c r="G111" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="4" t="n"/>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="6" t="n"/>
+      <c r="G112" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n"/>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="n"/>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="n"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="8" t="n"/>
-      <c r="G113" s="8" t="n">
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="n">
         <v>0</v>
       </c>
     </row>
